--- a/artfynd/A 59873-2025 artfynd.xlsx
+++ b/artfynd/A 59873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130242564</v>
       </c>
       <c r="B2" t="n">
-        <v>91883</v>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59873-2025 artfynd.xlsx
+++ b/artfynd/A 59873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130242564</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>91973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59873-2025 artfynd.xlsx
+++ b/artfynd/A 59873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130242564</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>91999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59873-2025 artfynd.xlsx
+++ b/artfynd/A 59873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130242564</v>
       </c>
       <c r="B2" t="n">
-        <v>91999</v>
+        <v>92000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59873-2025 artfynd.xlsx
+++ b/artfynd/A 59873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130242564</v>
       </c>
       <c r="B2" t="n">
-        <v>92000</v>
+        <v>92001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59873-2025 artfynd.xlsx
+++ b/artfynd/A 59873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130242564</v>
       </c>
       <c r="B2" t="n">
-        <v>92001</v>
+        <v>92003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59873-2025 artfynd.xlsx
+++ b/artfynd/A 59873-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130242564</v>
       </c>
       <c r="B2" t="n">
-        <v>92003</v>
+        <v>92152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
